--- a/historico_recap.xlsx
+++ b/historico_recap.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://petrobrasbr-my.sharepoint.com/personal/pedro_klauber_prestserv_petrobras_com_br1/Documents/C3/Banco de dados/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="395" documentId="8_{A2D22092-61F7-40F8-A3CB-EE4C820708D1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0860EF60-9B90-4987-B208-94F1B97CD634}"/>
+  <xr:revisionPtr revIDLastSave="443" documentId="8_{A2D22092-61F7-40F8-A3CB-EE4C820708D1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E98A4F81-FF38-49CB-B424-A0F74B21A30D}"/>
   <bookViews>
-    <workbookView xWindow="-105" yWindow="-16200" windowWidth="14610" windowHeight="15585" firstSheet="4" activeTab="9" xr2:uid="{764A3B1C-4385-41E0-85B9-B2E5043E601B}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="8" activeTab="9" xr2:uid="{764A3B1C-4385-41E0-85B9-B2E5043E601B}"/>
   </bookViews>
   <sheets>
     <sheet name="LISTA DE INDICADORES" sheetId="8" r:id="rId1"/>
@@ -49,7 +49,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="500" uniqueCount="136">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="510" uniqueCount="138">
   <si>
     <t>DATA</t>
   </si>
@@ -457,6 +457,12 @@
   </si>
   <si>
     <t>2025.30</t>
+  </si>
+  <si>
+    <t>2025.40</t>
+  </si>
+  <si>
+    <t>2025.31</t>
   </si>
 </sst>
 </file>
@@ -1338,7 +1344,7 @@
   <sheetPr codeName="Planilha10">
     <tabColor theme="4"/>
   </sheetPr>
-  <dimension ref="A1:C68"/>
+  <dimension ref="A1:C69"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="10.33203125" style="6" bestFit="1" customWidth="1"/>
@@ -2091,6 +2097,17 @@
         <v>1</v>
       </c>
       <c r="C68" s="16">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="69" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A69" s="28" t="s">
+        <v>135</v>
+      </c>
+      <c r="B69" s="16">
+        <v>1</v>
+      </c>
+      <c r="C69" s="16">
         <v>1</v>
       </c>
     </row>
@@ -3660,7 +3677,7 @@
   <sheetPr codeName="Planilha2">
     <tabColor theme="6"/>
   </sheetPr>
-  <dimension ref="A1:I22"/>
+  <dimension ref="A1:I23"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="13.5546875" style="6" customWidth="1"/>
@@ -4226,13 +4243,13 @@
       </c>
     </row>
     <row r="22" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A22" s="6">
+      <c r="A22" s="9">
         <v>45860</v>
       </c>
-      <c r="B22" s="7" t="s">
+      <c r="B22" s="10" t="s">
         <v>133</v>
       </c>
-      <c r="C22" s="12">
+      <c r="C22" s="11">
         <v>252</v>
       </c>
       <c r="D22" s="11">
@@ -4251,6 +4268,35 @@
         <v>1</v>
       </c>
       <c r="I22" s="44" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="23" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A23" s="9">
+        <v>45867</v>
+      </c>
+      <c r="B23" s="10" t="s">
+        <v>136</v>
+      </c>
+      <c r="C23" s="11">
+        <v>250</v>
+      </c>
+      <c r="D23" s="11">
+        <v>6</v>
+      </c>
+      <c r="E23" s="11">
+        <v>0</v>
+      </c>
+      <c r="F23" s="42">
+        <v>1</v>
+      </c>
+      <c r="G23" s="19">
+        <v>0.98970000000000002</v>
+      </c>
+      <c r="H23" s="40">
+        <v>1</v>
+      </c>
+      <c r="I23" s="44" t="s">
         <v>107</v>
       </c>
     </row>
@@ -4540,7 +4586,7 @@
   <sheetPr codeName="Planilha4">
     <tabColor theme="6"/>
   </sheetPr>
-  <dimension ref="A1:E13"/>
+  <dimension ref="A1:E14"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="10.33203125" bestFit="1" customWidth="1"/>
@@ -4772,6 +4818,23 @@
         <v>106</v>
       </c>
     </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A14" s="9">
+        <v>45867</v>
+      </c>
+      <c r="B14" s="10" t="s">
+        <v>135</v>
+      </c>
+      <c r="C14" s="11">
+        <v>10</v>
+      </c>
+      <c r="D14" s="39">
+        <v>10</v>
+      </c>
+      <c r="E14" s="44" t="s">
+        <v>106</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
 </worksheet>
@@ -4782,7 +4845,7 @@
   <sheetPr codeName="Planilha5">
     <tabColor theme="6"/>
   </sheetPr>
-  <dimension ref="A1:E28"/>
+  <dimension ref="A1:E29"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="10.33203125" bestFit="1" customWidth="1"/>
@@ -4950,7 +5013,7 @@
         <v>45722</v>
       </c>
       <c r="B10" s="44" t="str">
-        <f t="shared" ref="B10:B28" si="0">CONCATENATE(YEAR(A10),".",_xlfn.ISOWEEKNUM(A10))</f>
+        <f t="shared" ref="B10:B29" si="0">CONCATENATE(YEAR(A10),".",_xlfn.ISOWEEKNUM(A10))</f>
         <v>2025.10</v>
       </c>
       <c r="C10" s="11">
@@ -5284,6 +5347,24 @@
         <v>50</v>
       </c>
       <c r="E28" s="44" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A29" s="9">
+        <v>45867</v>
+      </c>
+      <c r="B29" s="44" t="str">
+        <f t="shared" si="0"/>
+        <v>2025.31</v>
+      </c>
+      <c r="C29" s="11">
+        <v>78</v>
+      </c>
+      <c r="D29" s="34">
+        <v>50</v>
+      </c>
+      <c r="E29" s="44" t="s">
         <v>106</v>
       </c>
     </row>
@@ -5298,7 +5379,7 @@
   <sheetPr codeName="Planilha6">
     <tabColor theme="6"/>
   </sheetPr>
-  <dimension ref="A1:E29"/>
+  <dimension ref="A1:E30"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="10.33203125" bestFit="1" customWidth="1"/>
@@ -5813,6 +5894,23 @@
         <v>20</v>
       </c>
       <c r="E29" s="44" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A30" s="9">
+        <v>45867</v>
+      </c>
+      <c r="B30" s="10" t="s">
+        <v>137</v>
+      </c>
+      <c r="C30" s="11">
+        <v>32</v>
+      </c>
+      <c r="D30" s="34">
+        <v>20</v>
+      </c>
+      <c r="E30" s="44" t="s">
         <v>106</v>
       </c>
     </row>
@@ -5964,7 +6062,7 @@
   <sheetPr codeName="Planilha8">
     <tabColor theme="4"/>
   </sheetPr>
-  <dimension ref="A1:F60"/>
+  <dimension ref="A1:F61"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="9.109375" bestFit="1" customWidth="1"/>
@@ -6945,7 +7043,7 @@
         <v>35</v>
       </c>
       <c r="D49" s="19">
-        <f t="shared" ref="D49:D60" si="0">C49/B49</f>
+        <f t="shared" ref="D49:D61" si="0">C49/B49</f>
         <v>6.6287878787878785E-2</v>
       </c>
       <c r="E49" s="19">
@@ -7183,6 +7281,27 @@
         <v>1.0731999999999999</v>
       </c>
       <c r="F60" s="27">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="61" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A61" s="10" t="s">
+        <v>135</v>
+      </c>
+      <c r="B61" s="11">
+        <v>756</v>
+      </c>
+      <c r="C61" s="11">
+        <v>42</v>
+      </c>
+      <c r="D61" s="19">
+        <f t="shared" si="0"/>
+        <v>5.5555555555555552E-2</v>
+      </c>
+      <c r="E61" s="19">
+        <v>1.0642</v>
+      </c>
+      <c r="F61" s="27">
         <v>1</v>
       </c>
     </row>
@@ -7196,7 +7315,7 @@
   <sheetPr codeName="Planilha9">
     <tabColor theme="4"/>
   </sheetPr>
-  <dimension ref="A1:H60"/>
+  <dimension ref="A1:H61"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="10.33203125" style="6" bestFit="1" customWidth="1"/>
@@ -8176,6 +8295,22 @@
       <c r="G60" s="11"/>
       <c r="H60" s="11"/>
     </row>
+    <row r="61" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A61" s="28" t="s">
+        <v>135</v>
+      </c>
+      <c r="B61" s="11">
+        <v>3.87</v>
+      </c>
+      <c r="C61" s="11">
+        <v>10</v>
+      </c>
+      <c r="D61" s="11"/>
+      <c r="E61" s="11"/>
+      <c r="F61" s="11"/>
+      <c r="G61" s="11"/>
+      <c r="H61" s="11"/>
+    </row>
   </sheetData>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
 </worksheet>

--- a/historico_recap.xlsx
+++ b/historico_recap.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://petrobrasbr-my.sharepoint.com/personal/pedro_klauber_prestserv_petrobras_com_br1/Documents/C3/Banco de dados/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="443" documentId="8_{A2D22092-61F7-40F8-A3CB-EE4C820708D1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E98A4F81-FF38-49CB-B424-A0F74B21A30D}"/>
+  <xr:revisionPtr revIDLastSave="444" documentId="8_{A2D22092-61F7-40F8-A3CB-EE4C820708D1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{81B69B0F-659A-4BCE-B802-F6ACFC8E40F2}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="8" activeTab="9" xr2:uid="{764A3B1C-4385-41E0-85B9-B2E5043E601B}"/>
+    <workbookView xWindow="-120" yWindow="-16320" windowWidth="29040" windowHeight="15720" activeTab="5" xr2:uid="{764A3B1C-4385-41E0-85B9-B2E5043E601B}"/>
   </bookViews>
   <sheets>
     <sheet name="LISTA DE INDICADORES" sheetId="8" r:id="rId1"/>
@@ -5905,7 +5905,7 @@
         <v>137</v>
       </c>
       <c r="C30" s="11">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D30" s="34">
         <v>20</v>

--- a/historico_recap.xlsx
+++ b/historico_recap.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://petrobrasbr-my.sharepoint.com/personal/pedro_klauber_prestserv_petrobras_com_br1/Documents/C3/Banco de dados/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="444" documentId="8_{A2D22092-61F7-40F8-A3CB-EE4C820708D1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{81B69B0F-659A-4BCE-B802-F6ACFC8E40F2}"/>
+  <xr:revisionPtr revIDLastSave="483" documentId="8_{A2D22092-61F7-40F8-A3CB-EE4C820708D1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5FAC9FCC-65B2-4CD1-951F-DBDF273ACF52}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-16320" windowWidth="29040" windowHeight="15720" activeTab="5" xr2:uid="{764A3B1C-4385-41E0-85B9-B2E5043E601B}"/>
+    <workbookView xWindow="-120" yWindow="-16320" windowWidth="29040" windowHeight="15720" firstSheet="6" activeTab="10" xr2:uid="{764A3B1C-4385-41E0-85B9-B2E5043E601B}"/>
   </bookViews>
   <sheets>
     <sheet name="LISTA DE INDICADORES" sheetId="8" r:id="rId1"/>
@@ -49,7 +49,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="510" uniqueCount="138">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="520" uniqueCount="140">
   <si>
     <t>DATA</t>
   </si>
@@ -463,6 +463,12 @@
   </si>
   <si>
     <t>2025.31</t>
+  </si>
+  <si>
+    <t>2025.41</t>
+  </si>
+  <si>
+    <t>2025.32</t>
   </si>
 </sst>
 </file>
@@ -1344,7 +1350,7 @@
   <sheetPr codeName="Planilha10">
     <tabColor theme="4"/>
   </sheetPr>
-  <dimension ref="A1:C69"/>
+  <dimension ref="A1:C70"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="10.33203125" style="6" bestFit="1" customWidth="1"/>
@@ -2108,6 +2114,17 @@
         <v>1</v>
       </c>
       <c r="C69" s="16">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="70" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A70" s="28" t="s">
+        <v>137</v>
+      </c>
+      <c r="B70" s="16">
+        <v>1</v>
+      </c>
+      <c r="C70" s="16">
         <v>1</v>
       </c>
     </row>
@@ -3677,7 +3694,7 @@
   <sheetPr codeName="Planilha2">
     <tabColor theme="6"/>
   </sheetPr>
-  <dimension ref="A1:I23"/>
+  <dimension ref="A1:I24"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="13.5546875" style="6" customWidth="1"/>
@@ -4297,6 +4314,31 @@
         <v>1</v>
       </c>
       <c r="I23" s="44" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="24" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A24" s="9">
+        <v>45874</v>
+      </c>
+      <c r="B24" s="10" t="s">
+        <v>138</v>
+      </c>
+      <c r="C24" s="11">
+        <v>237</v>
+      </c>
+      <c r="D24" s="11"/>
+      <c r="E24" s="11"/>
+      <c r="F24" s="42">
+        <v>1</v>
+      </c>
+      <c r="G24" s="19">
+        <v>0.98480000000000001</v>
+      </c>
+      <c r="H24" s="40">
+        <v>1</v>
+      </c>
+      <c r="I24" s="44" t="s">
         <v>107</v>
       </c>
     </row>
@@ -4586,7 +4628,7 @@
   <sheetPr codeName="Planilha4">
     <tabColor theme="6"/>
   </sheetPr>
-  <dimension ref="A1:E14"/>
+  <dimension ref="A1:E15"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="10.33203125" bestFit="1" customWidth="1"/>
@@ -4835,6 +4877,23 @@
         <v>106</v>
       </c>
     </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A15" s="9">
+        <v>45874</v>
+      </c>
+      <c r="B15" s="10" t="s">
+        <v>137</v>
+      </c>
+      <c r="C15" s="11">
+        <v>12</v>
+      </c>
+      <c r="D15" s="39">
+        <v>10</v>
+      </c>
+      <c r="E15" s="44" t="s">
+        <v>106</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
 </worksheet>
@@ -4845,7 +4904,7 @@
   <sheetPr codeName="Planilha5">
     <tabColor theme="6"/>
   </sheetPr>
-  <dimension ref="A1:E29"/>
+  <dimension ref="A1:E30"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="10.33203125" bestFit="1" customWidth="1"/>
@@ -5013,7 +5072,7 @@
         <v>45722</v>
       </c>
       <c r="B10" s="44" t="str">
-        <f t="shared" ref="B10:B29" si="0">CONCATENATE(YEAR(A10),".",_xlfn.ISOWEEKNUM(A10))</f>
+        <f t="shared" ref="B10:B30" si="0">CONCATENATE(YEAR(A10),".",_xlfn.ISOWEEKNUM(A10))</f>
         <v>2025.10</v>
       </c>
       <c r="C10" s="11">
@@ -5365,6 +5424,24 @@
         <v>50</v>
       </c>
       <c r="E29" s="44" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A30" s="9">
+        <v>45874</v>
+      </c>
+      <c r="B30" s="44" t="str">
+        <f t="shared" si="0"/>
+        <v>2025.32</v>
+      </c>
+      <c r="C30" s="11">
+        <v>77</v>
+      </c>
+      <c r="D30" s="34">
+        <v>50</v>
+      </c>
+      <c r="E30" s="44" t="s">
         <v>106</v>
       </c>
     </row>
@@ -5379,7 +5456,7 @@
   <sheetPr codeName="Planilha6">
     <tabColor theme="6"/>
   </sheetPr>
-  <dimension ref="A1:E30"/>
+  <dimension ref="A1:E31"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="10.33203125" bestFit="1" customWidth="1"/>
@@ -5911,6 +5988,23 @@
         <v>20</v>
       </c>
       <c r="E30" s="44" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A31" s="9">
+        <v>45874</v>
+      </c>
+      <c r="B31" s="10" t="s">
+        <v>139</v>
+      </c>
+      <c r="C31" s="11">
+        <v>32</v>
+      </c>
+      <c r="D31" s="34">
+        <v>20</v>
+      </c>
+      <c r="E31" s="44" t="s">
         <v>106</v>
       </c>
     </row>
@@ -6062,7 +6156,7 @@
   <sheetPr codeName="Planilha8">
     <tabColor theme="4"/>
   </sheetPr>
-  <dimension ref="A1:F61"/>
+  <dimension ref="A1:F62"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="9.109375" bestFit="1" customWidth="1"/>
@@ -7043,7 +7137,7 @@
         <v>35</v>
       </c>
       <c r="D49" s="19">
-        <f t="shared" ref="D49:D61" si="0">C49/B49</f>
+        <f t="shared" ref="D49:D62" si="0">C49/B49</f>
         <v>6.6287878787878785E-2</v>
       </c>
       <c r="E49" s="19">
@@ -7302,6 +7396,27 @@
         <v>1.0642</v>
       </c>
       <c r="F61" s="27">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="62" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A62" s="10" t="s">
+        <v>137</v>
+      </c>
+      <c r="B62" s="11">
+        <v>792</v>
+      </c>
+      <c r="C62" s="11">
+        <v>46</v>
+      </c>
+      <c r="D62" s="19">
+        <f t="shared" si="0"/>
+        <v>5.808080808080808E-2</v>
+      </c>
+      <c r="E62" s="19">
+        <v>1.0871999999999999</v>
+      </c>
+      <c r="F62" s="27">
         <v>1</v>
       </c>
     </row>
@@ -7315,7 +7430,7 @@
   <sheetPr codeName="Planilha9">
     <tabColor theme="4"/>
   </sheetPr>
-  <dimension ref="A1:H61"/>
+  <dimension ref="A1:H62"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="10.33203125" style="6" bestFit="1" customWidth="1"/>
@@ -8311,6 +8426,22 @@
       <c r="G61" s="11"/>
       <c r="H61" s="11"/>
     </row>
+    <row r="62" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A62" s="28" t="s">
+        <v>137</v>
+      </c>
+      <c r="B62" s="11">
+        <v>4.3</v>
+      </c>
+      <c r="C62" s="11">
+        <v>10</v>
+      </c>
+      <c r="D62" s="11"/>
+      <c r="E62" s="11"/>
+      <c r="F62" s="11"/>
+      <c r="G62" s="11"/>
+      <c r="H62" s="11"/>
+    </row>
   </sheetData>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
 </worksheet>

--- a/historico_recap.xlsx
+++ b/historico_recap.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://petrobrasbr-my.sharepoint.com/personal/pedro_klauber_prestserv_petrobras_com_br1/Documents/C3/Banco de dados/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="483" documentId="8_{A2D22092-61F7-40F8-A3CB-EE4C820708D1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5FAC9FCC-65B2-4CD1-951F-DBDF273ACF52}"/>
+  <xr:revisionPtr revIDLastSave="526" documentId="8_{A2D22092-61F7-40F8-A3CB-EE4C820708D1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F5C37C09-2B36-4A6C-8533-8F088BDBC75E}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-16320" windowWidth="29040" windowHeight="15720" firstSheet="6" activeTab="10" xr2:uid="{764A3B1C-4385-41E0-85B9-B2E5043E601B}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="10" activeTab="10" xr2:uid="{764A3B1C-4385-41E0-85B9-B2E5043E601B}"/>
   </bookViews>
   <sheets>
     <sheet name="LISTA DE INDICADORES" sheetId="8" r:id="rId1"/>
@@ -49,7 +49,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="520" uniqueCount="140">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="530" uniqueCount="141">
   <si>
     <t>DATA</t>
   </si>
@@ -469,6 +469,9 @@
   </si>
   <si>
     <t>2025.32</t>
+  </si>
+  <si>
+    <t>2025.42</t>
   </si>
 </sst>
 </file>
@@ -1350,7 +1353,7 @@
   <sheetPr codeName="Planilha10">
     <tabColor theme="4"/>
   </sheetPr>
-  <dimension ref="A1:C70"/>
+  <dimension ref="A1:C71"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="10.33203125" style="6" bestFit="1" customWidth="1"/>
@@ -2125,6 +2128,17 @@
         <v>1</v>
       </c>
       <c r="C70" s="16">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="71" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A71" s="28" t="s">
+        <v>139</v>
+      </c>
+      <c r="B71" s="16">
+        <v>1</v>
+      </c>
+      <c r="C71" s="16">
         <v>1</v>
       </c>
     </row>
@@ -3694,7 +3708,7 @@
   <sheetPr codeName="Planilha2">
     <tabColor theme="6"/>
   </sheetPr>
-  <dimension ref="A1:I24"/>
+  <dimension ref="A1:I25"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="13.5546875" style="6" customWidth="1"/>
@@ -4339,6 +4353,31 @@
         <v>1</v>
       </c>
       <c r="I24" s="44" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="25" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A25" s="9">
+        <v>45881</v>
+      </c>
+      <c r="B25" s="10" t="s">
+        <v>140</v>
+      </c>
+      <c r="C25" s="11">
+        <v>242</v>
+      </c>
+      <c r="D25" s="11"/>
+      <c r="E25" s="11"/>
+      <c r="F25" s="42">
+        <v>1</v>
+      </c>
+      <c r="G25" s="19">
+        <v>0.98860000000000003</v>
+      </c>
+      <c r="H25" s="40">
+        <v>1</v>
+      </c>
+      <c r="I25" s="44" t="s">
         <v>107</v>
       </c>
     </row>
@@ -4628,7 +4667,7 @@
   <sheetPr codeName="Planilha4">
     <tabColor theme="6"/>
   </sheetPr>
-  <dimension ref="A1:E15"/>
+  <dimension ref="A1:E16"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="10.33203125" bestFit="1" customWidth="1"/>
@@ -4894,6 +4933,23 @@
         <v>106</v>
       </c>
     </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A16" s="9">
+        <v>45881</v>
+      </c>
+      <c r="B16" s="10" t="s">
+        <v>139</v>
+      </c>
+      <c r="C16" s="11">
+        <v>5</v>
+      </c>
+      <c r="D16" s="39">
+        <v>10</v>
+      </c>
+      <c r="E16" s="44" t="s">
+        <v>106</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
 </worksheet>
@@ -4904,7 +4960,7 @@
   <sheetPr codeName="Planilha5">
     <tabColor theme="6"/>
   </sheetPr>
-  <dimension ref="A1:E30"/>
+  <dimension ref="A1:E31"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="10.33203125" bestFit="1" customWidth="1"/>
@@ -5072,7 +5128,7 @@
         <v>45722</v>
       </c>
       <c r="B10" s="44" t="str">
-        <f t="shared" ref="B10:B30" si="0">CONCATENATE(YEAR(A10),".",_xlfn.ISOWEEKNUM(A10))</f>
+        <f t="shared" ref="B10:B31" si="0">CONCATENATE(YEAR(A10),".",_xlfn.ISOWEEKNUM(A10))</f>
         <v>2025.10</v>
       </c>
       <c r="C10" s="11">
@@ -5442,6 +5498,24 @@
         <v>50</v>
       </c>
       <c r="E30" s="44" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A31" s="9">
+        <v>45881</v>
+      </c>
+      <c r="B31" s="44" t="str">
+        <f t="shared" si="0"/>
+        <v>2025.33</v>
+      </c>
+      <c r="C31" s="11">
+        <v>79</v>
+      </c>
+      <c r="D31" s="34">
+        <v>50</v>
+      </c>
+      <c r="E31" s="44" t="s">
         <v>106</v>
       </c>
     </row>
@@ -5456,7 +5530,7 @@
   <sheetPr codeName="Planilha6">
     <tabColor theme="6"/>
   </sheetPr>
-  <dimension ref="A1:E31"/>
+  <dimension ref="A1:E32"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="10.33203125" bestFit="1" customWidth="1"/>
@@ -6005,6 +6079,23 @@
         <v>20</v>
       </c>
       <c r="E31" s="44" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A32" s="9">
+        <v>45881</v>
+      </c>
+      <c r="B32" s="10" t="s">
+        <v>139</v>
+      </c>
+      <c r="C32" s="11">
+        <v>33</v>
+      </c>
+      <c r="D32" s="34">
+        <v>20</v>
+      </c>
+      <c r="E32" s="44" t="s">
         <v>106</v>
       </c>
     </row>
@@ -6156,7 +6247,7 @@
   <sheetPr codeName="Planilha8">
     <tabColor theme="4"/>
   </sheetPr>
-  <dimension ref="A1:F62"/>
+  <dimension ref="A1:F63"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="9.109375" bestFit="1" customWidth="1"/>
@@ -7137,7 +7228,7 @@
         <v>35</v>
       </c>
       <c r="D49" s="19">
-        <f t="shared" ref="D49:D62" si="0">C49/B49</f>
+        <f t="shared" ref="D49:D63" si="0">C49/B49</f>
         <v>6.6287878787878785E-2</v>
       </c>
       <c r="E49" s="19">
@@ -7417,6 +7508,27 @@
         <v>1.0871999999999999</v>
       </c>
       <c r="F62" s="27">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="63" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A63" s="10" t="s">
+        <v>139</v>
+      </c>
+      <c r="B63" s="11">
+        <v>717</v>
+      </c>
+      <c r="C63" s="11">
+        <v>69</v>
+      </c>
+      <c r="D63" s="19">
+        <f t="shared" si="0"/>
+        <v>9.6234309623430964E-2</v>
+      </c>
+      <c r="E63" s="19">
+        <v>1.0593999999999999</v>
+      </c>
+      <c r="F63" s="27">
         <v>1</v>
       </c>
     </row>
@@ -7430,7 +7542,7 @@
   <sheetPr codeName="Planilha9">
     <tabColor theme="4"/>
   </sheetPr>
-  <dimension ref="A1:H62"/>
+  <dimension ref="A1:H63"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="10.33203125" style="6" bestFit="1" customWidth="1"/>
@@ -8442,6 +8554,22 @@
       <c r="G62" s="11"/>
       <c r="H62" s="11"/>
     </row>
+    <row r="63" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A63" s="28" t="s">
+        <v>139</v>
+      </c>
+      <c r="B63" s="11">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="C63" s="11">
+        <v>10</v>
+      </c>
+      <c r="D63" s="11"/>
+      <c r="E63" s="11"/>
+      <c r="F63" s="11"/>
+      <c r="G63" s="11"/>
+      <c r="H63" s="11"/>
+    </row>
   </sheetData>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
 </worksheet>

--- a/historico_recap.xlsx
+++ b/historico_recap.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28827"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28925"/>
   <workbookPr codeName="EstaPastaDeTrabalho" defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://petrobrasbr-my.sharepoint.com/personal/pedro_klauber_prestserv_petrobras_com_br1/Documents/C3/Banco de dados/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="526" documentId="8_{A2D22092-61F7-40F8-A3CB-EE4C820708D1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F5C37C09-2B36-4A6C-8533-8F088BDBC75E}"/>
+  <xr:revisionPtr revIDLastSave="566" documentId="8_{A2D22092-61F7-40F8-A3CB-EE4C820708D1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B4FA32B8-1B76-4198-BED5-95916A1CEA98}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="10" activeTab="10" xr2:uid="{764A3B1C-4385-41E0-85B9-B2E5043E601B}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="6" activeTab="9" xr2:uid="{764A3B1C-4385-41E0-85B9-B2E5043E601B}"/>
   </bookViews>
   <sheets>
     <sheet name="LISTA DE INDICADORES" sheetId="8" r:id="rId1"/>
@@ -49,7 +49,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="530" uniqueCount="141">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="539" uniqueCount="138">
   <si>
     <t>DATA</t>
   </si>
@@ -450,28 +450,19 @@
     <t>2025.29</t>
   </si>
   <si>
-    <t>2025.39</t>
-  </si>
-  <si>
     <t>2026.25</t>
   </si>
   <si>
     <t>2025.30</t>
   </si>
   <si>
-    <t>2025.40</t>
-  </si>
-  <si>
     <t>2025.31</t>
   </si>
   <si>
-    <t>2025.41</t>
-  </si>
-  <si>
     <t>2025.32</t>
   </si>
   <si>
-    <t>2025.42</t>
+    <t>2025.33</t>
   </si>
 </sst>
 </file>
@@ -1353,7 +1344,7 @@
   <sheetPr codeName="Planilha10">
     <tabColor theme="4"/>
   </sheetPr>
-  <dimension ref="A1:C71"/>
+  <dimension ref="A1:C72"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="10.33203125" style="6" bestFit="1" customWidth="1"/>
@@ -2111,7 +2102,7 @@
     </row>
     <row r="69" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A69" s="28" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="B69" s="16">
         <v>1</v>
@@ -2122,7 +2113,7 @@
     </row>
     <row r="70" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A70" s="28" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="B70" s="16">
         <v>1</v>
@@ -2133,12 +2124,23 @@
     </row>
     <row r="71" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A71" s="28" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
       <c r="B71" s="16">
         <v>1</v>
       </c>
       <c r="C71" s="16">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="72" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A72" s="28" t="s">
+        <v>137</v>
+      </c>
+      <c r="B72" s="16">
+        <v>1</v>
+      </c>
+      <c r="C72" s="16">
         <v>1</v>
       </c>
     </row>
@@ -3708,7 +3710,7 @@
   <sheetPr codeName="Planilha2">
     <tabColor theme="6"/>
   </sheetPr>
-  <dimension ref="A1:I25"/>
+  <dimension ref="A1:I26"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="13.5546875" style="6" customWidth="1"/>
@@ -4278,7 +4280,7 @@
         <v>45860</v>
       </c>
       <c r="B22" s="10" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="C22" s="11">
         <v>252</v>
@@ -4307,7 +4309,7 @@
         <v>45867</v>
       </c>
       <c r="B23" s="10" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="C23" s="11">
         <v>250</v>
@@ -4336,7 +4338,7 @@
         <v>45874</v>
       </c>
       <c r="B24" s="10" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="C24" s="11">
         <v>237</v>
@@ -4361,7 +4363,7 @@
         <v>45881</v>
       </c>
       <c r="B25" s="10" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="C25" s="11">
         <v>242</v>
@@ -4380,6 +4382,21 @@
       <c r="I25" s="44" t="s">
         <v>107</v>
       </c>
+    </row>
+    <row r="26" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A26" s="9">
+        <v>45887</v>
+      </c>
+      <c r="B26" s="10" t="s">
+        <v>137</v>
+      </c>
+      <c r="C26" s="11"/>
+      <c r="D26" s="11"/>
+      <c r="E26" s="11"/>
+      <c r="F26" s="42"/>
+      <c r="G26" s="19"/>
+      <c r="H26" s="40"/>
+      <c r="I26" s="44"/>
     </row>
   </sheetData>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
@@ -4654,7 +4671,7 @@
         <v>45860</v>
       </c>
       <c r="B10" s="53" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
     </row>
   </sheetData>
@@ -4667,7 +4684,7 @@
   <sheetPr codeName="Planilha4">
     <tabColor theme="6"/>
   </sheetPr>
-  <dimension ref="A1:E16"/>
+  <dimension ref="A1:E17"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="10.33203125" bestFit="1" customWidth="1"/>
@@ -4904,7 +4921,7 @@
         <v>45867</v>
       </c>
       <c r="B14" s="10" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="C14" s="11">
         <v>10</v>
@@ -4921,7 +4938,7 @@
         <v>45874</v>
       </c>
       <c r="B15" s="10" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="C15" s="11">
         <v>12</v>
@@ -4938,7 +4955,7 @@
         <v>45881</v>
       </c>
       <c r="B16" s="10" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
       <c r="C16" s="11">
         <v>5</v>
@@ -4947,6 +4964,23 @@
         <v>10</v>
       </c>
       <c r="E16" s="44" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A17" s="9">
+        <v>45887</v>
+      </c>
+      <c r="B17" s="10" t="s">
+        <v>137</v>
+      </c>
+      <c r="C17" s="11">
+        <v>5</v>
+      </c>
+      <c r="D17" s="39">
+        <v>10</v>
+      </c>
+      <c r="E17" s="44" t="s">
         <v>106</v>
       </c>
     </row>
@@ -4960,7 +4994,7 @@
   <sheetPr codeName="Planilha5">
     <tabColor theme="6"/>
   </sheetPr>
-  <dimension ref="A1:E31"/>
+  <dimension ref="A1:E32"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="10.33203125" bestFit="1" customWidth="1"/>
@@ -5128,7 +5162,7 @@
         <v>45722</v>
       </c>
       <c r="B10" s="44" t="str">
-        <f t="shared" ref="B10:B31" si="0">CONCATENATE(YEAR(A10),".",_xlfn.ISOWEEKNUM(A10))</f>
+        <f t="shared" ref="B10:B32" si="0">CONCATENATE(YEAR(A10),".",_xlfn.ISOWEEKNUM(A10))</f>
         <v>2025.10</v>
       </c>
       <c r="C10" s="11">
@@ -5516,6 +5550,24 @@
         <v>50</v>
       </c>
       <c r="E31" s="44" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A32" s="9">
+        <v>45887</v>
+      </c>
+      <c r="B32" s="44" t="str">
+        <f t="shared" si="0"/>
+        <v>2025.34</v>
+      </c>
+      <c r="C32" s="11">
+        <v>78</v>
+      </c>
+      <c r="D32" s="34">
+        <v>50</v>
+      </c>
+      <c r="E32" s="44" t="s">
         <v>106</v>
       </c>
     </row>
@@ -5530,7 +5582,7 @@
   <sheetPr codeName="Planilha6">
     <tabColor theme="6"/>
   </sheetPr>
-  <dimension ref="A1:E32"/>
+  <dimension ref="A1:E33"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="10.33203125" bestFit="1" customWidth="1"/>
@@ -6036,7 +6088,7 @@
         <v>45860</v>
       </c>
       <c r="B29" s="10" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="C29" s="11">
         <v>48</v>
@@ -6053,7 +6105,7 @@
         <v>45867</v>
       </c>
       <c r="B30" s="10" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="C30" s="11">
         <v>31</v>
@@ -6070,7 +6122,7 @@
         <v>45874</v>
       </c>
       <c r="B31" s="10" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
       <c r="C31" s="11">
         <v>32</v>
@@ -6087,7 +6139,7 @@
         <v>45881</v>
       </c>
       <c r="B32" s="10" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
       <c r="C32" s="11">
         <v>33</v>
@@ -6096,6 +6148,23 @@
         <v>20</v>
       </c>
       <c r="E32" s="44" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A33" s="9">
+        <v>45887</v>
+      </c>
+      <c r="B33" s="10" t="s">
+        <v>137</v>
+      </c>
+      <c r="C33" s="11">
+        <v>35</v>
+      </c>
+      <c r="D33" s="34">
+        <v>20</v>
+      </c>
+      <c r="E33" s="44" t="s">
         <v>106</v>
       </c>
     </row>
@@ -6247,7 +6316,7 @@
   <sheetPr codeName="Planilha8">
     <tabColor theme="4"/>
   </sheetPr>
-  <dimension ref="A1:F63"/>
+  <dimension ref="A1:F64"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="9.109375" bestFit="1" customWidth="1"/>
@@ -7228,7 +7297,7 @@
         <v>35</v>
       </c>
       <c r="D49" s="19">
-        <f t="shared" ref="D49:D63" si="0">C49/B49</f>
+        <f t="shared" ref="D49:D64" si="0">C49/B49</f>
         <v>6.6287878787878785E-2</v>
       </c>
       <c r="E49" s="19">
@@ -7471,7 +7540,7 @@
     </row>
     <row r="61" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A61" s="10" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="B61" s="11">
         <v>756</v>
@@ -7490,9 +7559,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="62" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A62" s="10" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="B62" s="11">
         <v>792</v>
@@ -7513,7 +7582,7 @@
     </row>
     <row r="63" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A63" s="10" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
       <c r="B63" s="11">
         <v>717</v>
@@ -7529,6 +7598,27 @@
         <v>1.0593999999999999</v>
       </c>
       <c r="F63" s="27">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="64" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A64" s="10" t="s">
+        <v>137</v>
+      </c>
+      <c r="B64" s="11">
+        <v>756</v>
+      </c>
+      <c r="C64" s="11">
+        <v>72</v>
+      </c>
+      <c r="D64" s="19">
+        <f t="shared" si="0"/>
+        <v>9.5238095238095233E-2</v>
+      </c>
+      <c r="E64" s="19">
+        <v>1.0823</v>
+      </c>
+      <c r="F64" s="27">
         <v>1</v>
       </c>
     </row>
@@ -7542,7 +7632,7 @@
   <sheetPr codeName="Planilha9">
     <tabColor theme="4"/>
   </sheetPr>
-  <dimension ref="A1:H63"/>
+  <dimension ref="A1:H64"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="10.33203125" style="6" bestFit="1" customWidth="1"/>
@@ -8524,7 +8614,7 @@
     </row>
     <row r="61" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A61" s="28" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="B61" s="11">
         <v>3.87</v>
@@ -8540,7 +8630,7 @@
     </row>
     <row r="62" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A62" s="28" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="B62" s="11">
         <v>4.3</v>
@@ -8556,7 +8646,7 @@
     </row>
     <row r="63" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A63" s="28" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
       <c r="B63" s="11">
         <v>4.0999999999999996</v>
@@ -8569,6 +8659,22 @@
       <c r="F63" s="11"/>
       <c r="G63" s="11"/>
       <c r="H63" s="11"/>
+    </row>
+    <row r="64" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A64" s="28" t="s">
+        <v>137</v>
+      </c>
+      <c r="B64" s="11">
+        <v>4.0199999999999996</v>
+      </c>
+      <c r="C64" s="11">
+        <v>10</v>
+      </c>
+      <c r="D64" s="11"/>
+      <c r="E64" s="11"/>
+      <c r="F64" s="11"/>
+      <c r="G64" s="11"/>
+      <c r="H64" s="11"/>
     </row>
   </sheetData>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>

--- a/historico_recap.xlsx
+++ b/historico_recap.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://petrobrasbr-my.sharepoint.com/personal/pedro_klauber_prestserv_petrobras_com_br1/Documents/C3/Banco de dados/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="566" documentId="8_{A2D22092-61F7-40F8-A3CB-EE4C820708D1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B4FA32B8-1B76-4198-BED5-95916A1CEA98}"/>
+  <xr:revisionPtr revIDLastSave="580" documentId="8_{A2D22092-61F7-40F8-A3CB-EE4C820708D1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{64ADA1A9-5350-42BE-A820-AD419686EA91}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="6" activeTab="9" xr2:uid="{764A3B1C-4385-41E0-85B9-B2E5043E601B}"/>
+    <workbookView xWindow="28695" yWindow="75" windowWidth="14610" windowHeight="15585" firstSheet="3" activeTab="5" xr2:uid="{764A3B1C-4385-41E0-85B9-B2E5043E601B}"/>
   </bookViews>
   <sheets>
     <sheet name="LISTA DE INDICADORES" sheetId="8" r:id="rId1"/>
@@ -49,7 +49,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="539" uniqueCount="138">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="543" uniqueCount="139">
   <si>
     <t>DATA</t>
   </si>
@@ -463,6 +463,9 @@
   </si>
   <si>
     <t>2025.33</t>
+  </si>
+  <si>
+    <t>2025.34</t>
   </si>
 </sst>
 </file>
@@ -4684,7 +4687,7 @@
   <sheetPr codeName="Planilha4">
     <tabColor theme="6"/>
   </sheetPr>
-  <dimension ref="A1:E17"/>
+  <dimension ref="A1:E18"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="10.33203125" bestFit="1" customWidth="1"/>
@@ -4984,6 +4987,23 @@
         <v>106</v>
       </c>
     </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A18" s="9">
+        <v>45895</v>
+      </c>
+      <c r="B18" s="10" t="s">
+        <v>138</v>
+      </c>
+      <c r="C18" s="11">
+        <v>6</v>
+      </c>
+      <c r="D18" s="39">
+        <v>10</v>
+      </c>
+      <c r="E18" s="44" t="s">
+        <v>106</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
 </worksheet>
@@ -4994,7 +5014,7 @@
   <sheetPr codeName="Planilha5">
     <tabColor theme="6"/>
   </sheetPr>
-  <dimension ref="A1:E32"/>
+  <dimension ref="A1:E33"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="10.33203125" bestFit="1" customWidth="1"/>
@@ -5162,7 +5182,7 @@
         <v>45722</v>
       </c>
       <c r="B10" s="44" t="str">
-        <f t="shared" ref="B10:B32" si="0">CONCATENATE(YEAR(A10),".",_xlfn.ISOWEEKNUM(A10))</f>
+        <f t="shared" ref="B10:B33" si="0">CONCATENATE(YEAR(A10),".",_xlfn.ISOWEEKNUM(A10))</f>
         <v>2025.10</v>
       </c>
       <c r="C10" s="11">
@@ -5570,6 +5590,18 @@
       <c r="E32" s="44" t="s">
         <v>106</v>
       </c>
+    </row>
+    <row r="33" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A33" s="9">
+        <v>45895</v>
+      </c>
+      <c r="B33" s="44" t="str">
+        <f t="shared" si="0"/>
+        <v>2025.35</v>
+      </c>
+      <c r="C33" s="11"/>
+      <c r="D33" s="34"/>
+      <c r="E33" s="44"/>
     </row>
   </sheetData>
   <phoneticPr fontId="5" type="noConversion"/>
@@ -5582,7 +5614,7 @@
   <sheetPr codeName="Planilha6">
     <tabColor theme="6"/>
   </sheetPr>
-  <dimension ref="A1:E33"/>
+  <dimension ref="A1:E34"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="10.33203125" bestFit="1" customWidth="1"/>
@@ -6165,6 +6197,23 @@
         <v>20</v>
       </c>
       <c r="E33" s="44" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A34" s="9">
+        <v>45895</v>
+      </c>
+      <c r="B34" s="10" t="s">
+        <v>137</v>
+      </c>
+      <c r="C34" s="11">
+        <v>34</v>
+      </c>
+      <c r="D34" s="34">
+        <v>20</v>
+      </c>
+      <c r="E34" s="44" t="s">
         <v>106</v>
       </c>
     </row>

--- a/historico_recap.xlsx
+++ b/historico_recap.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://petrobrasbr-my.sharepoint.com/personal/pedro_klauber_prestserv_petrobras_com_br1/Documents/C3/Banco de dados/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="580" documentId="8_{A2D22092-61F7-40F8-A3CB-EE4C820708D1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{64ADA1A9-5350-42BE-A820-AD419686EA91}"/>
+  <xr:revisionPtr revIDLastSave="591" documentId="8_{A2D22092-61F7-40F8-A3CB-EE4C820708D1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3543AF43-4DC5-40F8-BAA6-89482F8B3163}"/>
   <bookViews>
-    <workbookView xWindow="28695" yWindow="75" windowWidth="14610" windowHeight="15585" firstSheet="3" activeTab="5" xr2:uid="{764A3B1C-4385-41E0-85B9-B2E5043E601B}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="7" activeTab="7" xr2:uid="{764A3B1C-4385-41E0-85B9-B2E5043E601B}"/>
   </bookViews>
   <sheets>
     <sheet name="LISTA DE INDICADORES" sheetId="8" r:id="rId1"/>
@@ -49,7 +49,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="543" uniqueCount="139">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="546" uniqueCount="139">
   <si>
     <t>DATA</t>
   </si>
@@ -651,7 +651,7 @@
     <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="54">
+  <cellXfs count="55">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -778,6 +778,9 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="1" fontId="0" fillId="5" borderId="5" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="10" fontId="0" fillId="0" borderId="5" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1347,7 +1350,7 @@
   <sheetPr codeName="Planilha10">
     <tabColor theme="4"/>
   </sheetPr>
-  <dimension ref="A1:C72"/>
+  <dimension ref="A1:C73"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="10.33203125" style="6" bestFit="1" customWidth="1"/>
@@ -2144,6 +2147,17 @@
         <v>1</v>
       </c>
       <c r="C72" s="16">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="73" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A73" s="28" t="s">
+        <v>138</v>
+      </c>
+      <c r="B73" s="16">
+        <v>1</v>
+      </c>
+      <c r="C73" s="16">
         <v>1</v>
       </c>
     </row>
@@ -6365,7 +6379,7 @@
   <sheetPr codeName="Planilha8">
     <tabColor theme="4"/>
   </sheetPr>
-  <dimension ref="A1:F64"/>
+  <dimension ref="A1:F65"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="9.109375" bestFit="1" customWidth="1"/>
@@ -7671,6 +7685,17 @@
         <v>1</v>
       </c>
     </row>
+    <row r="65" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A65" s="53" t="s">
+        <v>138</v>
+      </c>
+      <c r="E65" s="54">
+        <v>1.0724</v>
+      </c>
+      <c r="F65" s="27">
+        <v>1</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
 </worksheet>
@@ -7681,7 +7706,7 @@
   <sheetPr codeName="Planilha9">
     <tabColor theme="4"/>
   </sheetPr>
-  <dimension ref="A1:H64"/>
+  <dimension ref="A1:H65"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="10.33203125" style="6" bestFit="1" customWidth="1"/>
@@ -8725,6 +8750,22 @@
       <c r="G64" s="11"/>
       <c r="H64" s="11"/>
     </row>
+    <row r="65" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A65" s="28" t="s">
+        <v>138</v>
+      </c>
+      <c r="B65" s="11">
+        <v>3.96</v>
+      </c>
+      <c r="C65" s="11">
+        <v>10</v>
+      </c>
+      <c r="D65" s="11"/>
+      <c r="E65" s="11"/>
+      <c r="F65" s="11"/>
+      <c r="G65" s="11"/>
+      <c r="H65" s="11"/>
+    </row>
   </sheetData>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
 </worksheet>

--- a/historico_recap.xlsx
+++ b/historico_recap.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://petrobrasbr-my.sharepoint.com/personal/pedro_klauber_prestserv_petrobras_com_br1/Documents/C3/Banco de dados/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="720" documentId="8_{A2D22092-61F7-40F8-A3CB-EE4C820708D1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8AD05AAC-F7CE-4714-8E96-31B83310E73C}"/>
+  <xr:revisionPtr revIDLastSave="721" documentId="8_{A2D22092-61F7-40F8-A3CB-EE4C820708D1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E04E8857-D526-4440-A29F-753F4D5B64B4}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-45" windowWidth="29040" windowHeight="15720" firstSheet="11" activeTab="12" xr2:uid="{764A3B1C-4385-41E0-85B9-B2E5043E601B}"/>
+    <workbookView xWindow="28680" yWindow="-45" windowWidth="29040" windowHeight="15720" firstSheet="3" activeTab="10" xr2:uid="{764A3B1C-4385-41E0-85B9-B2E5043E601B}"/>
   </bookViews>
   <sheets>
     <sheet name="BD_Plano_IE" sheetId="17" r:id="rId1"/>
@@ -38858,7 +38858,7 @@
     <row r="2" spans="1:5" s="12" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A2" s="62">
         <f ca="1">TODAY()</f>
-        <v>45901</v>
+        <v>45902</v>
       </c>
       <c r="B2" s="63" t="str">
         <f ca="1">CONCATENATE(YEAR(A2),".",_xlfn.ISOWEEKNUM(A2))</f>
@@ -39483,7 +39483,7 @@
     <row r="2" spans="1:5" s="12" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A2" s="62">
         <f ca="1">TODAY()</f>
-        <v>45901</v>
+        <v>45902</v>
       </c>
       <c r="B2" s="63" t="str">
         <f ca="1">CONCATENATE(YEAR(A2),".",_xlfn.ISOWEEKNUM(A2))</f>
@@ -40084,7 +40084,7 @@
         <v>3496</v>
       </c>
       <c r="C36" s="11">
-        <v>43</v>
+        <v>32</v>
       </c>
       <c r="D36" s="34">
         <v>20</v>
@@ -91746,7 +91746,7 @@
     <row r="2" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A2" s="55">
         <f ca="1">TODAY()</f>
-        <v>45901</v>
+        <v>45902</v>
       </c>
       <c r="B2" s="56">
         <f ca="1">_xlfn.ISOWEEKNUM(A2)</f>
@@ -92370,7 +92370,7 @@
     <row r="2" spans="1:5" s="12" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A2" s="62">
         <f ca="1">TODAY()</f>
-        <v>45901</v>
+        <v>45902</v>
       </c>
       <c r="B2" s="63" t="str">
         <f ca="1">CONCATENATE(YEAR(A2),".",_xlfn.ISOWEEKNUM(A2))</f>

--- a/historico_recap.xlsx
+++ b/historico_recap.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://petrobrasbr-my.sharepoint.com/personal/pedro_klauber_prestserv_petrobras_com_br1/Documents/C3/Banco de dados/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="721" documentId="8_{A2D22092-61F7-40F8-A3CB-EE4C820708D1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E04E8857-D526-4440-A29F-753F4D5B64B4}"/>
+  <xr:revisionPtr revIDLastSave="726" documentId="8_{A2D22092-61F7-40F8-A3CB-EE4C820708D1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1B5F4D79-EC54-4A5C-BCFD-470BC288CFFB}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-45" windowWidth="29040" windowHeight="15720" firstSheet="3" activeTab="10" xr2:uid="{764A3B1C-4385-41E0-85B9-B2E5043E601B}"/>
   </bookViews>
@@ -40030,7 +40030,7 @@
         <v>45881</v>
       </c>
       <c r="B33" s="10" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="C33" s="11">
         <v>33</v>
@@ -40047,7 +40047,7 @@
         <v>45887</v>
       </c>
       <c r="B34" s="10" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="C34" s="11">
         <v>35</v>
@@ -40064,7 +40064,7 @@
         <v>45895</v>
       </c>
       <c r="B35" s="10" t="s">
-        <v>137</v>
+        <v>3497</v>
       </c>
       <c r="C35" s="11">
         <v>34</v>
